--- a/results/Int Task Remove ACC -0.7/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_9_permute.xlsx
@@ -440,47 +440,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6433118635420793</v>
+        <v>0.6298862515019903</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6447239022883955</v>
+        <v>0.6300866287616886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6447239022883955</v>
+        <v>0.6340010337721271</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6384934113808913</v>
+        <v>0.634061616846458</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6360655572635918</v>
+        <v>0.645762876840148</v>
       </c>
     </row>
     <row r="7">
@@ -490,837 +490,837 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6310792849519027</v>
+        <v>0.6448168746517732</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6306505044673725</v>
+        <v>0.6424076485711792</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6408512844954319</v>
+        <v>0.6409210976780404</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6465924118440749</v>
+        <v>0.6445651444260215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6498451020010875</v>
+        <v>0.6490620531788494</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6547102081641147</v>
+        <v>0.6541275366015749</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6660620666044613</v>
+        <v>0.6655448449006169</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6660620666044613</v>
+        <v>0.6735554041444864</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6527530895689707</v>
+        <v>0.6936166249353892</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6376732743053923</v>
+        <v>0.6860019534265518</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6279757869086857</v>
+        <v>0.6860019534265518</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6408934073532078</v>
+        <v>0.686323496834912</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6580377461082507</v>
+        <v>0.6867242513543086</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6577162026998906</v>
+        <v>0.6778469010331009</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.667441716061731</v>
+        <v>0.673023749907699</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6637137592384993</v>
+        <v>0.6712156556061999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6509265350509166</v>
+        <v>0.6653300351079755</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6616676959635897</v>
+        <v>0.6617091475407635</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.653396176385691</v>
+        <v>0.661187226872705</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6360004430451973</v>
+        <v>0.6634752868046372</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6360004430451973</v>
+        <v>0.6651016318831435</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6326685417771483</v>
+        <v>0.5946378105511885</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6326685417771483</v>
+        <v>0.5916227537272856</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6419746725828863</v>
+        <v>0.5770324698427189</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6483682846766777</v>
+        <v>0.5677263390369809</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.621079385643993</v>
+        <v>0.5750191314971571</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6132925306607415</v>
+        <v>0.5842787761212064</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6326502493807437</v>
+        <v>0.5842787761212064</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.621750834066148</v>
+        <v>0.5831929797474642</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6348082486960374</v>
+        <v>0.6111160711288925</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6789712960414583</v>
+        <v>0.6424875309628177</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6800151373775752</v>
+        <v>0.6252779101692298</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.682098121085595</v>
+        <v>0.6360658929038927</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.676356993736952</v>
+        <v>0.6498036504239137</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6759562392175553</v>
+        <v>0.6587415838194524</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6587283260275627</v>
+        <v>0.6386567003873289</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6255306473158845</v>
+        <v>0.5990741362296854</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6177763494418302</v>
+        <v>0.6190658794782807</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6207121951546966</v>
+        <v>0.5805410857292457</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6497254462337803</v>
+        <v>0.6360606904792272</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6604716417509684</v>
+        <v>0.6184410850579651</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6548283535500674</v>
+        <v>0.619867052876773</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6565525377763159</v>
+        <v>0.6187486993938336</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6571117145177856</v>
+        <v>0.628162067275742</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6558674959219704</v>
+        <v>0.6210045378568696</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6381455202089026</v>
+        <v>0.6204826171888111</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6411931341420027</v>
+        <v>0.6418070202525357</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6437094294786163</v>
+        <v>0.6156591304231082</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6478055837120476</v>
+        <v>0.6147178271989475</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5948588296893985</v>
+        <v>0.602042539051749</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5589721687062409</v>
+        <v>0.6442717948029456</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5523875772811793</v>
+        <v>0.6317409998053286</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5565209875880217</v>
+        <v>0.6361867234122536</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5448010995576261</v>
+        <v>0.604078700937779</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5382212070967785</v>
+        <v>0.6032771918989857</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5147814310359874</v>
+        <v>0.5960167887278561</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4982664178453236</v>
+        <v>0.6172339547154106</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4982664178453236</v>
+        <v>0.6251886298491632</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4998927629238298</v>
+        <v>0.6213906920231727</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.497586074955192</v>
+        <v>0.625300398069397</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4993288872181461</v>
+        <v>0.6342754197181963</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4998088528485792</v>
+        <v>0.6342754197181963</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4986438453638005</v>
+        <v>0.6418993213353114</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4978609643617128</v>
+        <v>0.6706610100087937</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4962765743208319</v>
+        <v>0.6843334854902698</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4946688572790312</v>
+        <v>0.6948420476743484</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4961601071363841</v>
+        <v>0.6879870979868294</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4961601071363841</v>
+        <v>0.6964365069242594</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4912950009733569</v>
+        <v>0.6964365069242594</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4894635796709383</v>
+        <v>0.6964365069242594</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4911318797870698</v>
+        <v>0.6888641260933484</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4915140062697608</v>
+        <v>0.7054163953574233</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4915140062697608</v>
+        <v>0.6609509361007995</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4915140062697608</v>
+        <v>0.6615940229175198</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4912530459357316</v>
+        <v>0.6615940229175198</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4931450503124811</v>
+        <v>0.6429443374124817</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4923015862360625</v>
+        <v>0.5331090696722136</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4941096805375615</v>
+        <v>0.5203312434130591</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4941096805375615</v>
+        <v>0.526277614805765</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4944312239459216</v>
+        <v>0.5291062234424612</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5207600238975895</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.5138585880283818</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5138585880283818</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.5028005826715626</v>
       </c>
     </row>
   </sheetData>
